--- a/data information/Authorization Configuration/Authorization Configuration.xlsx
+++ b/data information/Authorization Configuration/Authorization Configuration.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Punch Item List\data information\Authorized Configuration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Punch Item List\data information\Authorization Configuration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9644E069-83F9-4E56-8690-3CD8B6EE69AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B058B321-B1FD-451E-A656-587AE0556D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C211A79F-D66A-4DD8-AC7F-238765CB0DCC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="44">
   <si>
     <t>Role/Group</t>
   </si>
@@ -114,13 +114,72 @@
   </si>
   <si>
     <t>Setting</t>
+  </si>
+  <si>
+    <t>Submit to OE
+(By Discipline)</t>
+  </si>
+  <si>
+    <t>Submit to Owner
+(By Discipline)</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>Superadmin</t>
+  </si>
+  <si>
+    <t>Create Project</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Role Group</t>
+  </si>
+  <si>
+    <t>Package &amp; System</t>
+  </si>
+  <si>
+    <t>Disciplines</t>
+  </si>
+  <si>
+    <t>Authorized Rule</t>
+  </si>
+  <si>
+    <t>Notification</t>
+  </si>
+  <si>
+    <t>Database Backup</t>
+  </si>
+  <si>
+    <t>Factory Reset</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>Full Access</t>
+  </si>
+  <si>
+    <t>Project Setting</t>
+  </si>
+  <si>
+    <t>Restricted</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>As per package</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,16 +193,53 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -166,11 +262,328 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -178,14 +591,141 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -515,388 +1055,790 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{102AEC2A-809A-4CD6-BA90-6F8669165DE8}">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" customWidth="1"/>
-    <col min="4" max="4" width="17.54296875" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.81640625" customWidth="1"/>
-    <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.90625" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="17.6328125" customWidth="1"/>
+    <col min="30" max="30" width="17.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:30" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2" t="s">
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Y1" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="AB1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="AC1" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="1:30" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="27"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="27"/>
     </row>
-    <row r="3" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3" t="s">
+    <row r="3" spans="1:30" s="1" customFormat="1" ht="28" x14ac:dyDescent="0.35">
+      <c r="A3" s="27"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="N3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="O3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="P3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="Q3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="R3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="U3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="V3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="W3" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="27"/>
     </row>
-    <row r="4" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:30" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="X4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC4" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD4" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="T4" s="3" t="s">
+      <c r="B5" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="X5" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y5" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z5" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB5" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC5" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD5" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="6" spans="1:30" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="W6" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="X6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z6" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC6" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD6" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T5" s="3" t="s">
+      <c r="B7" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="W7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="X7" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z7" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA7" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC7" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD7" s="24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+    <row r="8" spans="1:30" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T6" s="3" t="s">
+      <c r="B8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="W8" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="X8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA8" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB8" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC8" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD8" s="24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="1" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+    <row r="9" spans="1:30" s="1" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="T7" s="3" t="s">
+      <c r="B9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="T9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="V9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="W9" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="X9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA9" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC9" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD9" s="25" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="23">
+    <mergeCell ref="Y1:Y3"/>
+    <mergeCell ref="Z1:Z3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="X1:X3"/>
+    <mergeCell ref="AD1:AD3"/>
+    <mergeCell ref="AB1:AB3"/>
+    <mergeCell ref="AA1:AA3"/>
+    <mergeCell ref="R2:W2"/>
+    <mergeCell ref="K1:W1"/>
+    <mergeCell ref="AC1:AC3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="M2:Q2"/>
     <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="P1:P3"/>
-    <mergeCell ref="T1:T3"/>
-    <mergeCell ref="S1:S3"/>
-    <mergeCell ref="R1:R3"/>
-    <mergeCell ref="Q1:Q3"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="C1:O1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B4:AD9">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",B4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",B4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
